--- a/research/traditional_assets/database/data/pakistan/pakistan_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.0492</v>
+        <v>0.00116</v>
       </c>
       <c r="E2">
-        <v>0.0172</v>
+        <v>0.0158</v>
       </c>
       <c r="G2">
-        <v>0.249003984063745</v>
+        <v>0.4019370460048427</v>
       </c>
       <c r="H2">
-        <v>0.249003984063745</v>
+        <v>0.4019370460048427</v>
       </c>
       <c r="I2">
-        <v>0.3050763789159379</v>
+        <v>0.4467797954526747</v>
       </c>
       <c r="J2">
-        <v>0.2116164723591505</v>
+        <v>0.3038102609078188</v>
       </c>
       <c r="K2">
-        <v>8.779999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="L2">
-        <v>0.1749003984063745</v>
+        <v>0.3123486682808717</v>
       </c>
       <c r="M2">
-        <v>4.07</v>
+        <v>3.15</v>
       </c>
       <c r="N2">
-        <v>0.1068241469816273</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="O2">
-        <v>0.4635535307517085</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="P2">
-        <v>4.07</v>
+        <v>3.15</v>
       </c>
       <c r="Q2">
-        <v>0.1068241469816273</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="R2">
-        <v>0.4635535307517085</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>7.4</v>
+        <v>10.7</v>
       </c>
       <c r="V2">
-        <v>0.1942257217847769</v>
+        <v>0.3919413919413919</v>
       </c>
       <c r="W2">
-        <v>0.1444078947368421</v>
+        <v>0.2193877551020408</v>
       </c>
       <c r="X2">
-        <v>0.1742448672469342</v>
+        <v>0.2607002165147891</v>
       </c>
       <c r="Y2">
-        <v>-0.02983697251009212</v>
+        <v>-0.04131246141274825</v>
       </c>
       <c r="Z2">
-        <v>0.8980349492106379</v>
+        <v>0.759834070974287</v>
       </c>
       <c r="AA2">
-        <v>0.1900389880071841</v>
+        <v>0.2308453873493482</v>
       </c>
       <c r="AB2">
-        <v>0.1652323469312102</v>
+        <v>0.2458476519538874</v>
       </c>
       <c r="AC2">
-        <v>0.02480664107597383</v>
+        <v>-0.01500226460453924</v>
       </c>
       <c r="AD2">
-        <v>0.164</v>
+        <v>0.128</v>
       </c>
       <c r="AE2">
-        <v>2.975828892099595</v>
+        <v>2.789972239022692</v>
       </c>
       <c r="AF2">
-        <v>3.139828892099595</v>
+        <v>2.917972239022693</v>
       </c>
       <c r="AG2">
-        <v>-4.260171107900405</v>
+        <v>-7.782027760977307</v>
       </c>
       <c r="AH2">
-        <v>0.07613583704032048</v>
+        <v>0.09656413130377094</v>
       </c>
       <c r="AI2">
-        <v>0.05069159776933255</v>
+        <v>0.04727913334096439</v>
       </c>
       <c r="AJ2">
-        <v>-0.1258922177616272</v>
+        <v>-0.3987108735311415</v>
       </c>
       <c r="AK2">
-        <v>-0.07811119313059516</v>
+        <v>-0.1525350267650383</v>
       </c>
       <c r="AL2">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AM2">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AN2">
-        <v>0.01024359775140537</v>
+        <v>0.006698063840920985</v>
       </c>
       <c r="AO2">
-        <v>846.6666666666666</v>
+        <v>1436.363636363636</v>
       </c>
       <c r="AP2">
-        <v>-0.2660943852529922</v>
+        <v>-0.4072228027722296</v>
       </c>
       <c r="AQ2">
-        <v>846.6666666666666</v>
+        <v>1436.363636363636</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.0492</v>
+        <v>0.00116</v>
       </c>
       <c r="E3">
-        <v>0.0172</v>
+        <v>0.0158</v>
       </c>
       <c r="G3">
-        <v>0.249003984063745</v>
+        <v>0.4019370460048427</v>
       </c>
       <c r="H3">
-        <v>0.249003984063745</v>
+        <v>0.4019370460048427</v>
       </c>
       <c r="I3">
-        <v>0.3050763789159379</v>
+        <v>0.4467797954526747</v>
       </c>
       <c r="J3">
-        <v>0.2116164723591505</v>
+        <v>0.3038102609078188</v>
       </c>
       <c r="K3">
-        <v>8.779999999999999</v>
+        <v>12.9</v>
       </c>
       <c r="L3">
-        <v>0.1749003984063745</v>
+        <v>0.3123486682808717</v>
       </c>
       <c r="M3">
-        <v>4.07</v>
+        <v>3.15</v>
       </c>
       <c r="N3">
-        <v>0.1068241469816273</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="O3">
-        <v>0.4635535307517085</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="P3">
-        <v>4.07</v>
+        <v>3.15</v>
       </c>
       <c r="Q3">
-        <v>0.1068241469816273</v>
+        <v>0.1153846153846154</v>
       </c>
       <c r="R3">
-        <v>0.4635535307517085</v>
+        <v>0.2441860465116279</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>7.4</v>
+        <v>10.7</v>
       </c>
       <c r="V3">
-        <v>0.1942257217847769</v>
+        <v>0.3919413919413919</v>
       </c>
       <c r="W3">
-        <v>0.1444078947368421</v>
+        <v>0.2193877551020408</v>
       </c>
       <c r="X3">
-        <v>0.1742448672469342</v>
+        <v>0.2607002165147891</v>
       </c>
       <c r="Y3">
-        <v>-0.02983697251009212</v>
+        <v>-0.04131246141274825</v>
       </c>
       <c r="Z3">
-        <v>0.8980349492106379</v>
+        <v>0.759834070974287</v>
       </c>
       <c r="AA3">
-        <v>0.1900389880071841</v>
+        <v>0.2308453873493482</v>
       </c>
       <c r="AB3">
-        <v>0.1652323469312102</v>
+        <v>0.2458476519538874</v>
       </c>
       <c r="AC3">
-        <v>0.02480664107597383</v>
+        <v>-0.01500226460453924</v>
       </c>
       <c r="AD3">
-        <v>0.164</v>
+        <v>0.128</v>
       </c>
       <c r="AE3">
-        <v>2.975828892099595</v>
+        <v>2.789972239022692</v>
       </c>
       <c r="AF3">
-        <v>3.139828892099595</v>
+        <v>2.917972239022693</v>
       </c>
       <c r="AG3">
-        <v>-4.260171107900405</v>
+        <v>-7.782027760977307</v>
       </c>
       <c r="AH3">
-        <v>0.07613583704032048</v>
+        <v>0.09656413130377094</v>
       </c>
       <c r="AI3">
-        <v>0.05069159776933255</v>
+        <v>0.04727913334096439</v>
       </c>
       <c r="AJ3">
-        <v>-0.1258922177616272</v>
+        <v>-0.3987108735311415</v>
       </c>
       <c r="AK3">
-        <v>-0.07811119313059516</v>
+        <v>-0.1525350267650383</v>
       </c>
       <c r="AL3">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AM3">
-        <v>0.015</v>
+        <v>0.011</v>
       </c>
       <c r="AN3">
-        <v>0.01024359775140537</v>
+        <v>0.006698063840920985</v>
       </c>
       <c r="AO3">
-        <v>846.6666666666666</v>
+        <v>1436.363636363636</v>
       </c>
       <c r="AP3">
-        <v>-0.2660943852529922</v>
+        <v>-0.4072228027722296</v>
       </c>
       <c r="AQ3">
-        <v>846.6666666666666</v>
+        <v>1436.363636363636</v>
       </c>
     </row>
   </sheetData>

--- a/research/traditional_assets/database/data/pakistan/pakistan_reinsurance.xlsx
+++ b/research/traditional_assets/database/data/pakistan/pakistan_reinsurance.xlsx
@@ -588,46 +588,46 @@
         </is>
       </c>
       <c r="D2">
-        <v>0.00116</v>
+        <v>0.175</v>
       </c>
       <c r="E2">
-        <v>0.0158</v>
+        <v>0.627</v>
       </c>
       <c r="G2">
-        <v>0.4019370460048427</v>
+        <v>0.3667481662591687</v>
       </c>
       <c r="H2">
-        <v>0.4019370460048427</v>
+        <v>0.3667481662591687</v>
       </c>
       <c r="I2">
-        <v>0.4467797954526747</v>
+        <v>0.4026625672407883</v>
       </c>
       <c r="J2">
-        <v>0.3038102609078188</v>
+        <v>0.2899170484133676</v>
       </c>
       <c r="K2">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="L2">
-        <v>0.3123486682808717</v>
+        <v>0.2811735941320294</v>
       </c>
       <c r="M2">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="N2">
-        <v>0.1153846153846154</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="O2">
-        <v>0.2441860465116279</v>
+        <v>0.2034782608695652</v>
       </c>
       <c r="P2">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="Q2">
-        <v>0.1153846153846154</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="R2">
-        <v>0.2441860465116279</v>
+        <v>0.2034782608695652</v>
       </c>
       <c r="S2">
         <v>0</v>
@@ -636,73 +636,73 @@
         <v>0</v>
       </c>
       <c r="U2">
-        <v>10.7</v>
+        <v>17.3</v>
       </c>
       <c r="V2">
-        <v>0.3919413919413919</v>
+        <v>0.6920000000000001</v>
       </c>
       <c r="W2">
-        <v>0.2193877551020408</v>
+        <v>0.195578231292517</v>
       </c>
       <c r="X2">
-        <v>0.2607002165147891</v>
+        <v>0.2577309503719073</v>
       </c>
       <c r="Y2">
-        <v>-0.04131246141274825</v>
+        <v>-0.06215271907939027</v>
       </c>
       <c r="Z2">
-        <v>0.759834070974287</v>
+        <v>0.8117736152060421</v>
       </c>
       <c r="AA2">
-        <v>0.2308453873493482</v>
+        <v>0.2353470105003845</v>
       </c>
       <c r="AB2">
-        <v>0.2458476519538874</v>
+        <v>0.2458707283942679</v>
       </c>
       <c r="AC2">
-        <v>-0.01500226460453924</v>
+        <v>-0.0105237178938834</v>
       </c>
       <c r="AD2">
-        <v>0.128</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE2">
-        <v>2.789972239022692</v>
+        <v>2.15550499925879</v>
       </c>
       <c r="AF2">
-        <v>2.917972239022693</v>
+        <v>2.23950499925879</v>
       </c>
       <c r="AG2">
-        <v>-7.782027760977307</v>
+        <v>-15.06049500074121</v>
       </c>
       <c r="AH2">
-        <v>0.09656413130377094</v>
+        <v>0.08221533391740152</v>
       </c>
       <c r="AI2">
-        <v>0.04727913334096439</v>
+        <v>0.03967974204040593</v>
       </c>
       <c r="AJ2">
-        <v>-0.3987108735311415</v>
+        <v>-1.515215798157384</v>
       </c>
       <c r="AK2">
-        <v>-0.1525350267650383</v>
+        <v>-0.384790124479766</v>
       </c>
       <c r="AL2">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="AM2">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="AN2">
-        <v>0.006698063840920985</v>
+        <v>0.004912280701754386</v>
       </c>
       <c r="AO2">
-        <v>1436.363636363636</v>
+        <v>800.0000000000001</v>
       </c>
       <c r="AP2">
-        <v>-0.4072228027722296</v>
+        <v>-0.8807307017977316</v>
       </c>
       <c r="AQ2">
-        <v>1436.363636363636</v>
+        <v>800.0000000000001</v>
       </c>
     </row>
     <row r="3">
@@ -722,46 +722,46 @@
         </is>
       </c>
       <c r="D3">
-        <v>0.00116</v>
+        <v>0.175</v>
       </c>
       <c r="E3">
-        <v>0.0158</v>
+        <v>0.627</v>
       </c>
       <c r="G3">
-        <v>0.4019370460048427</v>
+        <v>0.3667481662591687</v>
       </c>
       <c r="H3">
-        <v>0.4019370460048427</v>
+        <v>0.3667481662591687</v>
       </c>
       <c r="I3">
-        <v>0.4467797954526747</v>
+        <v>0.4026625672407883</v>
       </c>
       <c r="J3">
-        <v>0.3038102609078188</v>
+        <v>0.2899170484133676</v>
       </c>
       <c r="K3">
-        <v>12.9</v>
+        <v>11.5</v>
       </c>
       <c r="L3">
-        <v>0.3123486682808717</v>
+        <v>0.2811735941320294</v>
       </c>
       <c r="M3">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="N3">
-        <v>0.1153846153846154</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="O3">
-        <v>0.2441860465116279</v>
+        <v>0.2034782608695652</v>
       </c>
       <c r="P3">
-        <v>3.15</v>
+        <v>2.34</v>
       </c>
       <c r="Q3">
-        <v>0.1153846153846154</v>
+        <v>0.09359999999999999</v>
       </c>
       <c r="R3">
-        <v>0.2441860465116279</v>
+        <v>0.2034782608695652</v>
       </c>
       <c r="S3">
         <v>0</v>
@@ -770,73 +770,73 @@
         <v>0</v>
       </c>
       <c r="U3">
-        <v>10.7</v>
+        <v>17.3</v>
       </c>
       <c r="V3">
-        <v>0.3919413919413919</v>
+        <v>0.6920000000000001</v>
       </c>
       <c r="W3">
-        <v>0.2193877551020408</v>
+        <v>0.195578231292517</v>
       </c>
       <c r="X3">
-        <v>0.2607002165147891</v>
+        <v>0.2577309503719073</v>
       </c>
       <c r="Y3">
-        <v>-0.04131246141274825</v>
+        <v>-0.06215271907939027</v>
       </c>
       <c r="Z3">
-        <v>0.759834070974287</v>
+        <v>0.8117736152060421</v>
       </c>
       <c r="AA3">
-        <v>0.2308453873493482</v>
+        <v>0.2353470105003845</v>
       </c>
       <c r="AB3">
-        <v>0.2458476519538874</v>
+        <v>0.2458707283942679</v>
       </c>
       <c r="AC3">
-        <v>-0.01500226460453924</v>
+        <v>-0.0105237178938834</v>
       </c>
       <c r="AD3">
-        <v>0.128</v>
+        <v>0.08400000000000001</v>
       </c>
       <c r="AE3">
-        <v>2.789972239022692</v>
+        <v>2.15550499925879</v>
       </c>
       <c r="AF3">
-        <v>2.917972239022693</v>
+        <v>2.23950499925879</v>
       </c>
       <c r="AG3">
-        <v>-7.782027760977307</v>
+        <v>-15.06049500074121</v>
       </c>
       <c r="AH3">
-        <v>0.09656413130377094</v>
+        <v>0.08221533391740152</v>
       </c>
       <c r="AI3">
-        <v>0.04727913334096439</v>
+        <v>0.03967974204040593</v>
       </c>
       <c r="AJ3">
-        <v>-0.3987108735311415</v>
+        <v>-1.515215798157384</v>
       </c>
       <c r="AK3">
-        <v>-0.1525350267650383</v>
+        <v>-0.384790124479766</v>
       </c>
       <c r="AL3">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="AM3">
-        <v>0.011</v>
+        <v>0.018</v>
       </c>
       <c r="AN3">
-        <v>0.006698063840920985</v>
+        <v>0.004912280701754386</v>
       </c>
       <c r="AO3">
-        <v>1436.363636363636</v>
+        <v>800.0000000000001</v>
       </c>
       <c r="AP3">
-        <v>-0.4072228027722296</v>
+        <v>-0.8807307017977316</v>
       </c>
       <c r="AQ3">
-        <v>1436.363636363636</v>
+        <v>800.0000000000001</v>
       </c>
     </row>
   </sheetData>
